--- a/data/05_modelado/results/results_arboles.xlsx
+++ b/data/05_modelado/results/results_arboles.xlsx
@@ -563,7 +563,7 @@
         <v>0.8914335247012511</v>
       </c>
       <c r="K2" t="n">
-        <v>78.515</v>
+        <v>11.375</v>
       </c>
       <c r="L2" t="n">
         <v>6.64</v>
@@ -628,7 +628,7 @@
         <v>0.8973080152679669</v>
       </c>
       <c r="K3" t="n">
-        <v>22.354</v>
+        <v>9.34</v>
       </c>
       <c r="L3" t="n">
         <v>6.64</v>
@@ -693,10 +693,10 @@
         <v>0.8860051515220626</v>
       </c>
       <c r="K4" t="n">
-        <v>14.862</v>
+        <v>8.473000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>6.64</v>
+        <v>6.78</v>
       </c>
       <c r="M4" t="n">
         <v>0.8159</v>
@@ -758,10 +758,10 @@
         <v>0.8757806104007668</v>
       </c>
       <c r="K5" t="n">
-        <v>35.522</v>
+        <v>3.791</v>
       </c>
       <c r="L5" t="n">
-        <v>6.64</v>
+        <v>6.79</v>
       </c>
       <c r="M5" t="n">
         <v>0.761</v>
@@ -823,7 +823,7 @@
         <v>0.8629535208863327</v>
       </c>
       <c r="K6" t="n">
-        <v>2.793</v>
+        <v>3.808</v>
       </c>
       <c r="L6" t="n">
         <v>6.64</v>
@@ -888,7 +888,7 @@
         <v>0.8667458469568079</v>
       </c>
       <c r="K7" t="n">
-        <v>34.249</v>
+        <v>5.966</v>
       </c>
       <c r="L7" t="n">
         <v>6.65</v>
@@ -953,10 +953,10 @@
         <v>0.8416865049334774</v>
       </c>
       <c r="K8" t="n">
-        <v>16.298</v>
+        <v>3.281</v>
       </c>
       <c r="L8" t="n">
-        <v>6.64</v>
+        <v>6.78</v>
       </c>
       <c r="M8" t="n">
         <v>0.7613</v>
@@ -1018,7 +1018,7 @@
         <v>0.8530261771131158</v>
       </c>
       <c r="K9" t="n">
-        <v>2.588</v>
+        <v>2.989</v>
       </c>
       <c r="L9" t="n">
         <v>6.91</v>
@@ -1083,10 +1083,10 @@
         <v>0.8217955618400345</v>
       </c>
       <c r="K10" t="n">
-        <v>2.813</v>
+        <v>2.478</v>
       </c>
       <c r="L10" t="n">
-        <v>6.64</v>
+        <v>6.78</v>
       </c>
       <c r="M10" t="n">
         <v>0.7453</v>
